--- a/output/2026-09-06_00_Slovenia_Podravska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-06_00_Slovenia_Podravska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Negozio specializzato in utensili per falegnameria/carpenteria, rivenditore Metabo.</t>
+          <t>Negozio specializzato in utensili per falegnameria/carpenteria, rivenditore Metabo. [DUPLICATO — vedi anche: 2026-09-05_23_Slovenia_Podravska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,6 @@
           <t>Janžekovič Robert s.p. - Prodajalna "Orodje"</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Ptuj</t>
@@ -826,10 +825,9 @@
           <t>02 333 8900</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Catena generalista fai-da-te/edilizia con reparto utensili. Non specialista di settore: valutare idoneita' come partner B2B specializzato.</t>
+          <t>Catena generalista fai-da-te/edilizia con reparto utensili. Non specialista di settore: valutare idoneita' come partner B2B specializzato. [DUPLICATO — vedi anche: 2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -864,10 +862,9 @@
           <t>02 798 0600</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Stessa catena generalista fai-da-te/edilizia di Merkur Maribor, punto vendita di Ptuj.</t>
+          <t>Stessa catena generalista fai-da-te/edilizia di Merkur Maribor, punto vendita di Ptuj. [DUPLICATO — vedi anche: 2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/output/2026-09-06_00_Slovenia_Podravska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-06_00_Slovenia_Podravska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
